--- a/site/User-Integration-V5-Setup-Guide/headings.xlsx
+++ b/site/User-Integration-V5-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,20 +2311,86 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>Integration Logs</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>h_01M1B2BZ41065XG0H41AZSYK8Y</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-V5-Setup-Guide/#h_01M1B2BZ41065XG0H41AZSYK8Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Parameters in User Integration V3</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>h_01M1B2DKK08B01F03ZSC8FSVZB</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-V5-Setup-Guide/#h_01M1B2DKK08B01F03ZSC8FSVZB</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Parameters in User Integration V4 and V5</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>h_01M1B2EGP89V5H4EGNP7YKYHPG</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-V5-Setup-Guide/#h_01M1B2EGP89V5H4EGNP7YKYHPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-V5-Setup-Guide/#h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
